--- a/shipment_data/ship_price.xlsx
+++ b/shipment_data/ship_price.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
   <si>
     <t>仓库名</t>
   </si>
@@ -39,9 +39,6 @@
     <t>九方</t>
   </si>
   <si>
-    <t>赤道</t>
-  </si>
-  <si>
     <t>联宇</t>
   </si>
   <si>
@@ -51,22 +48,25 @@
     <t>报关费</t>
   </si>
   <si>
+    <t>AVP1</t>
+  </si>
+  <si>
     <t>MEM1</t>
   </si>
   <si>
+    <t>FTW1</t>
+  </si>
+  <si>
+    <t>ONT8</t>
+  </si>
+  <si>
+    <t>FWA4</t>
+  </si>
+  <si>
+    <t>TEB9</t>
+  </si>
+  <si>
     <t>LAS1</t>
-  </si>
-  <si>
-    <t>ABE8</t>
-  </si>
-  <si>
-    <t>GYR2</t>
-  </si>
-  <si>
-    <t>SMF3</t>
-  </si>
-  <si>
-    <t>TEB9</t>
   </si>
   <si>
     <t>SBD1</t>
@@ -1238,10 +1238,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="6" outlineLevelCol="5"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="6" outlineLevelCol="4"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1257,13 +1257,10 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="B2" s="1">
         <v>150</v>
@@ -1272,104 +1269,76 @@
         <v>200</v>
       </c>
       <c r="D2" s="1">
+        <v>100</v>
+      </c>
+      <c r="E2" s="1">
         <v>150</v>
       </c>
-      <c r="E2" s="1">
-        <v>100</v>
-      </c>
-      <c r="F2" s="1">
-        <v>150</v>
-      </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1">
+        <v>6.3</v>
+      </c>
+      <c r="C3" s="1">
+        <v>7.2</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1">
-        <v>7.5</v>
-      </c>
-      <c r="C3" s="1">
-        <v>6.6</v>
-      </c>
-      <c r="D3" s="1">
-        <v>6.72</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1">
-        <v>5.7</v>
-      </c>
+      <c r="B4" s="1">
+        <v>7.4</v>
+      </c>
+      <c r="C4" s="1">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1" t="s">
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="1">
-        <v>5.7</v>
-      </c>
-      <c r="C4" s="1">
+      <c r="B5" s="1">
+        <v>7.2</v>
+      </c>
+      <c r="C5" s="1">
+        <v>8</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="1">
         <v>5.3</v>
       </c>
-      <c r="D4" s="1">
-        <v>5.17</v>
-      </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1">
-        <v>3.7</v>
-      </c>
+      <c r="C6" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="1">
-        <v>5.4</v>
-      </c>
-      <c r="C5" s="1">
-        <v>5.4</v>
-      </c>
-      <c r="D5" s="1">
-        <v>5.4</v>
-      </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="1" t="s">
+    <row r="7" spans="1:5">
+      <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="1">
-        <v>5.8</v>
-      </c>
-      <c r="C6" s="1">
-        <v>5.5</v>
-      </c>
-      <c r="D6" s="1">
-        <v>5.22</v>
-      </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="B7" s="1">
-        <v>5.5</v>
+        <v>6.7</v>
       </c>
       <c r="C7" s="1">
-        <v>5.5</v>
-      </c>
-      <c r="D7" s="1">
-        <v>4.75</v>
-      </c>
+        <v>7.9</v>
+      </c>
+      <c r="D7" s="1"/>
       <c r="E7" s="1"/>
-      <c r="F7" s="1">
-        <v>3.8</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1380,10 +1349,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="6" outlineLevelCol="3"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="6" outlineLevelCol="4"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1394,12 +1363,12 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1">
         <v>150</v>
@@ -1411,78 +1380,94 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="C3" s="1">
+        <v>5.98</v>
+      </c>
+      <c r="D3" s="1">
+        <v>5.2</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="1">
-        <v>5.2</v>
-      </c>
-      <c r="C3" s="1">
-        <v>4.96</v>
-      </c>
-      <c r="D3" s="1">
-        <v>5</v>
+      <c r="B4" s="1">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1">
+        <v>5.85</v>
+      </c>
+      <c r="D4" s="1">
+        <v>5.6</v>
+      </c>
+      <c r="E4">
+        <v>6.4</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="1">
-        <v>5.5</v>
-      </c>
-      <c r="C4" s="1">
-        <v>4.62</v>
-      </c>
-      <c r="D4" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="1">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="C5" s="1">
-        <v>4.62</v>
+        <v>5.51</v>
       </c>
       <c r="D5" s="1">
-        <v>3.4</v>
+        <v>4.9</v>
+      </c>
+      <c r="E5">
+        <v>5.7</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="1">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="C6" s="1">
-        <v>5.1</v>
+        <v>5.51</v>
       </c>
       <c r="D6" s="1">
-        <v>3.4</v>
+        <v>4.9</v>
+      </c>
+      <c r="E6">
+        <v>5.7</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="1">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="C7" s="1">
-        <v>5.37</v>
+        <v>6.26</v>
       </c>
       <c r="D7" s="1">
-        <v>4.9</v>
+        <v>6</v>
+      </c>
+      <c r="E7">
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>